--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1339 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A56891D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,12 +436,12 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,17 +1050,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1042,13 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1108,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1149,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1318,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1651,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1762,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1873,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1984,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2095,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2206,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2317,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2378,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2428,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2489,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2539,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2600,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2650,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2711,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2761,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2822,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2872,1125 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -989,36 +989,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1026,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1050,37 +1046,33 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>166.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1105,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1141,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1235,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1268,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1292,17 +1288,17 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1312,13 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3994,6 +3994,117 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1346,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1490,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1712,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,32 +1806,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1823,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1847,33 +1867,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1925,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq47，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1934,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1942,10 +1966,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置浦建路锦绣路 ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2045,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2234,12 +2274,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2267,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2275,10 +2315,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 6分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2378,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,7 +2878,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,7 +2989,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3100,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3155,7 +3211,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3266,7 +3322,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3377,7 +3433,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3488,7 +3544,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3599,7 +3655,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3710,7 +3766,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3778,7 +3834,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3821,7 +3877,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3835,7 +3891,7 @@
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3936,7 +3992,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3998,22 +4054,22 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4051,7 +4107,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4095,13 +4151,699 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr"/>
-      <c r="AC32" s="2" t="inlineStr">
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1584,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1617,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1695,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>181分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1728,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1752,33 +1764,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1816,24 +1832,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1843,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1946,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq47，推进10站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq57，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1958,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2052,32 +2068,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2085,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2109,33 +2129,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2163,32 +2187,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2196,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2220,33 +2248,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2311,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq60，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2307,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2434,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2505,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2545,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2584,7 +2616,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2656,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,7 +2727,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2767,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2845,32 +2877,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2878,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2902,33 +2938,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2989,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3211,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3584,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,7 +3695,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3806,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,7 +3917,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3931,7 +3971,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3992,7 +4032,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4107,7 +4147,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4222,7 +4262,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4333,7 +4373,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4444,7 +4484,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4498,7 +4538,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4599,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4613,7 +4653,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4714,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4728,7 +4768,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4736,22 +4776,22 @@
       <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4784,12 +4824,12 @@
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4803,47 +4843,1066 @@
       <c r="T38" s="2" t="inlineStr"/>
       <c r="U38" s="2" t="inlineStr">
         <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W38" s="2" t="inlineStr">
+      <c r="W39" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X38" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y38" s="2" t="inlineStr">
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z38" s="2" t="inlineStr">
+      <c r="Z39" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
+      <c r="AA39" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>5/28</t>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A56891D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,18 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1431,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2278,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2577,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2688,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2799,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2914,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2996,32 +3000,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -3029,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3053,33 +3061,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3107,32 +3119,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3140,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3164,17 +3180,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3184,13 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3290,7 +3310,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3329,32 +3349,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -3362,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3386,33 +3410,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3551,32 +3579,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3584,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3608,17 +3640,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3628,13 +3660,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3734,7 +3770,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3773,32 +3809,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3806,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3830,33 +3870,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3884,32 +3928,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3917,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3941,17 +3989,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3961,17 +4009,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3999,32 +4047,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4032,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4056,17 +4108,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4076,17 +4128,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4186,7 +4238,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4201,7 +4253,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4229,32 +4281,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4262,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4286,33 +4342,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4340,12 +4400,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq29推进至seq50，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4373,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4381,10 +4441,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>09:30</t>
@@ -4484,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4538,7 +4614,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4566,32 +4642,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4599,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4623,17 +4703,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4643,17 +4723,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4768,7 +4848,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4883,7 +4963,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4944,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4998,7 +5078,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5113,7 +5193,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5228,7 +5308,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5343,7 +5423,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5484,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5515,7 +5595,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5626,7 +5706,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5737,7 +5817,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5848,7 +5928,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5902,7 +5982,804 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
           <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1545,22 +1545,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2272,17 +2272,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2514,13 +2514,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2631,7 +2635,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2735,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2742,7 +2746,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2857,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3321,7 +3325,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3440,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3555,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3781,7 +3785,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3900,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4253,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4372,7 +4376,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4409,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq29推进至seq50，推进21站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq29推进至seq62，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4433,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4499,7 +4503,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4614,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4664,12 +4668,12 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4679,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4733,7 +4737,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4761,32 +4765,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4794,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4818,37 +4826,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4948,7 +4956,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4963,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4991,32 +4999,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -5024,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5048,17 +5060,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5068,17 +5080,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5193,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5221,32 +5233,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5254,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5278,37 +5294,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5336,32 +5352,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5369,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5393,17 +5413,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5413,17 +5433,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5451,32 +5471,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5484,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5508,17 +5532,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5528,13 +5552,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5645,7 +5673,7 @@
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5734,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5756,7 +5784,7 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5845,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5856,7 +5884,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5867,7 +5895,7 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5956,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5982,7 +6010,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6071,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6097,7 +6125,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6186,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6212,7 +6240,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6301,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6323,7 +6351,7 @@
       <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6412,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6438,7 +6466,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6527,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6549,7 +6577,7 @@
       <c r="AB52" s="2" t="inlineStr"/>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6638,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6664,7 +6692,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6753,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6779,7 +6807,685 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A56891D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2624,18 +2624,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2740,13 +2744,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,13 +2859,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2966,17 +2978,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,22 +3092,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3226,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,18 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3434,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,18 +3790,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4257,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4376,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4856,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4971,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5324,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5481,24 +5501,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5508,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5557,12 +5577,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5590,32 +5610,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5623,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5647,33 +5671,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5701,32 +5729,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5734,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5758,17 +5790,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5778,13 +5810,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5812,32 +5848,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5845,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5869,17 +5909,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5889,13 +5929,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5923,32 +5967,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5956,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5980,17 +6028,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6000,17 +6048,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6038,32 +6086,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6071,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6095,37 +6147,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6153,32 +6205,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -6186,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6210,17 +6266,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6230,17 +6286,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6268,32 +6324,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6301,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6325,33 +6385,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6379,32 +6443,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6412,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6436,17 +6504,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6456,17 +6524,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6494,32 +6562,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6527,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6551,33 +6623,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB52" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6692,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6807,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6922,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6983,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7094,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7148,7 +7224,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7263,7 +7339,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7435,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7479,13 +7555,588 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr"/>
-      <c r="AC60" s="2" t="inlineStr">
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
         <is>
           <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6572,24 +6572,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6681,32 +6681,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6714,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6738,17 +6742,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6758,17 +6762,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6868,7 +6872,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6944,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7059,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7170,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7285,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7400,7 +7404,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7511,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7626,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7737,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7852,7 +7856,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7967,7 +7971,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8016,12 +8020,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8086,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8140,6 +8144,236 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1664,22 +1664,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4386,17 +4386,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6572,12 +6572,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6800,32 +6800,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6833,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6857,17 +6861,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6877,17 +6881,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6915,32 +6919,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6948,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6972,17 +6980,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6992,17 +7000,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7038,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7063,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7071,10 +7079,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7141,32 +7165,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -7174,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7198,37 +7226,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7343,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7443,7 +7471,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7515,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7630,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7741,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7856,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7971,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8020,12 +8048,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8114,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8140,7 +8168,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8245,17 +8273,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8344,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8374,6 +8402,347 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2038,13 +2038,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2163,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2524,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2700,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3107,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3345,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3464,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4043,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4396,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,7 +4516,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4638,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4757,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5214,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5225,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5344,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5885,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6177,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6300,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6415,7 +6419,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6538,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6653,7 +6657,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6891,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7047,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7071,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7187,12 +7191,12 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7202,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7260,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7371,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7399,32 +7403,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7432,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7456,17 +7464,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7476,13 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7597,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7769,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7823,7 +7835,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7999,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8053,7 +8065,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8168,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8283,7 +8295,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8398,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8513,7 +8525,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8586,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8628,7 +8640,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8733,13 +8745,243 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr"/>
-      <c r="AC70" s="2" t="inlineStr">
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
         <is>
           <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2157,17 +2157,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2271,14 +2271,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2407,13 +2407,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2633,17 +2637,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2748,17 +2752,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3111,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3215,14 +3219,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>155.0</t>
@@ -3230,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3335,17 +3339,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3579,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3809,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4527,7 +4531,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4761,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4995,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5229,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5338,17 +5342,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,14 +5456,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
@@ -5467,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5695,17 +5699,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5933,17 +5937,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6181,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6409,17 +6413,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6657,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6895,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7145,7 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7260,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7288,32 +7292,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7321,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,17 +7353,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7365,17 +7373,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7413,12 +7421,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -7440,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7489,12 +7497,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7522,32 +7530,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7555,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,17 +7591,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7599,17 +7611,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7637,32 +7649,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7670,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7694,17 +7710,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7714,13 +7730,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7748,32 +7768,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7781,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7805,17 +7829,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7825,17 +7849,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7863,32 +7887,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7896,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7920,17 +7948,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7940,17 +7968,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8065,7 +8093,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8180,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8295,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8410,7 +8438,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8525,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8640,7 +8668,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8750,12 +8778,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8866,7 +8894,7 @@
       <c r="AB71" s="2" t="inlineStr"/>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8981,7 +9009,348 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>130.5</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1902,14 +1902,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>139.5</t>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3105,17 +3105,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3453,14 +3453,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>136.5</t>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,14 +3683,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3803,12 +3803,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,14 +4155,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>130.5</t>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,14 +5103,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>139.5</t>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,14 +6289,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>136.5</t>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6889,17 +6889,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7897,12 +7897,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8006,32 +8006,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8039,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,17 +8067,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8083,12 +8087,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8121,32 +8125,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -8154,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,17 +8186,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8198,17 +8206,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8236,32 +8244,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8269,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,17 +8305,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8313,17 +8325,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8351,32 +8363,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8384,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8408,17 +8424,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8428,17 +8444,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8553,7 +8569,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8729,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8844,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8955,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9070,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9185,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9239,7 +9255,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9247,22 +9263,22 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9295,12 +9311,12 @@
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9314,43 +9330,1078 @@
       <c r="T75" s="2" t="inlineStr"/>
       <c r="U75" s="2" t="inlineStr">
         <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
           <t>16:08</t>
         </is>
       </c>
-      <c r="V75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W75" s="2" t="inlineStr">
+      <c r="W76" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X75" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y75" s="2" t="inlineStr">
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z75" s="2" t="inlineStr">
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr"/>
-      <c r="AC75" s="2" t="inlineStr">
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
         <is>
           <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2038,17 +2038,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7254,17 +7254,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8135,24 +8135,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8254,24 +8254,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8373,12 +8373,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8439,22 +8439,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8482,32 +8482,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8515,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8539,17 +8543,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8559,17 +8563,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8597,32 +8601,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8630,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8654,37 +8662,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8712,32 +8720,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -8745,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8769,17 +8781,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8789,17 +8801,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8827,12 +8839,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq41，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8860,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8868,10 +8880,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8938,32 +8966,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -8971,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8995,17 +9027,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9015,12 +9047,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9053,32 +9085,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9086,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9110,17 +9146,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9130,17 +9166,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9255,7 +9291,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9370,7 +9406,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9542,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9596,7 +9632,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9657,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9772,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9826,7 +9862,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10002,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10117,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10171,7 +10207,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10286,7 +10322,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10401,7 +10437,812 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A56891D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
           <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>165.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2407,17 +2407,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,17 +3219,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>165.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7730,17 +7730,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq41，推进13站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8976,24 +8976,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>165.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9161,17 +9161,17 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9319,32 +9319,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9352,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9376,37 +9380,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9545,32 +9549,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9578,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,17 +9610,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9622,17 +9630,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9808,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9923,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9962,7 +9970,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9977,7 +9985,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10046,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10153,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10268,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10322,7 +10330,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10383,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10498,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10552,7 +10560,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10728,7 +10736,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10843,7 +10851,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10958,7 +10966,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11012,7 +11020,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11081,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11188,7 +11196,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11246,6 +11254,811 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>165.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,22 +1307,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3453,22 +3453,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,22 +5103,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,17 +5580,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,22 +5813,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,22 +6289,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,22 +6527,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,17 +6770,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9668,32 +9668,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9701,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9725,37 +9729,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9783,32 +9787,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -9816,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9840,37 +9848,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9898,32 +9906,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9931,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9955,17 +9967,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9975,17 +9987,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10013,32 +10025,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10046,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10070,37 +10086,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10128,32 +10144,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10161,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10185,37 +10205,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10243,32 +10263,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10276,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,17 +10324,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10320,17 +10344,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10358,32 +10382,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -10391,7 +10419,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10415,37 +10443,37 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA84" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10560,7 +10588,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10588,32 +10616,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10621,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10645,17 +10677,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10665,17 +10697,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10790,7 +10822,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10905,7 +10937,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11020,7 +11052,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11135,7 +11167,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11196,7 +11228,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11250,7 +11282,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11343,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11365,7 +11397,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11458,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11480,7 +11512,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11573,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11595,7 +11627,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11688,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11710,7 +11742,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11803,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11886,7 +11918,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11948,22 +11980,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -11996,12 +12028,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12015,47 +12047,852 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>138.3</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W98" s="2" t="inlineStr">
+      <c r="W99" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X98" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y98" s="2" t="inlineStr">
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z98" s="2" t="inlineStr">
+      <c r="Z99" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA98" s="2" t="inlineStr">
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>134.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB98" s="2" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="AC98" s="2" t="inlineStr">
-        <is>
-          <t>8/30</t>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>141.7</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AC108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2157,17 +2157,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2752,17 +2752,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3339,17 +3339,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4874,17 +4874,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,17 +5342,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6413,17 +6413,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7008,17 +7008,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7373,17 +7373,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7611,17 +7611,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7849,17 +7849,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8444,17 +8444,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8682,17 +8682,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10501,32 +10501,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10534,7 +10538,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10558,17 +10562,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10578,17 +10582,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10626,24 +10630,24 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10653,7 +10657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10692,7 +10696,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10702,12 +10706,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10735,32 +10739,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10768,7 +10776,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10792,17 +10800,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10812,17 +10820,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10850,32 +10858,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10883,7 +10895,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10907,17 +10919,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10927,17 +10939,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10965,32 +10977,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10998,7 +11014,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11022,17 +11038,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11042,17 +11058,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11080,32 +11096,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11113,7 +11133,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11137,17 +11157,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11157,17 +11177,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11215,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11228,7 +11252,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11252,17 +11276,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11272,17 +11296,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11367,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11397,7 +11421,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11497,7 +11521,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11573,7 +11597,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11688,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11742,7 +11766,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11827,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11918,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12033,7 +12057,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12087,7 +12111,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12172,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12202,7 +12226,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12287,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12378,7 +12402,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12432,7 +12456,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12517,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12547,7 +12571,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12608,7 +12632,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12723,7 +12747,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12777,7 +12801,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -12785,22 +12809,22 @@
       <c r="A105" s="2" t="inlineStr"/>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -12833,12 +12857,12 @@
       <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12852,47 +12876,392 @@
       <c r="T105" s="2" t="inlineStr"/>
       <c r="U105" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W105" s="2" t="inlineStr">
+      <c r="W106" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X105" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y105" s="2" t="inlineStr">
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z105" s="2" t="inlineStr">
+      <c r="Z106" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA105" s="2" t="inlineStr">
+      <c r="AA106" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB105" s="2" t="inlineStr">
+      <c r="AB106" s="2" t="inlineStr">
         <is>
           <t>141.7</t>
         </is>
       </c>
-      <c r="AC105" s="2" t="inlineStr">
+      <c r="AC106" s="2" t="inlineStr">
         <is>
           <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>157.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>157.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5461,17 +5461,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9047,12 +9047,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>157.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9166,17 +9166,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9281,17 +9281,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9400,17 +9400,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9987,17 +9987,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10949,7 +10949,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11187,7 +11187,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11564,32 +11564,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11597,7 +11601,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11621,17 +11625,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11641,17 +11645,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -11679,32 +11683,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11712,7 +11720,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11736,17 +11744,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11756,12 +11764,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11794,32 +11802,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11827,7 +11839,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11851,17 +11863,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11871,17 +11883,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11909,32 +11921,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -11942,7 +11958,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11966,17 +11982,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11986,12 +12002,12 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>157.7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12024,12 +12040,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12057,7 +12073,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12065,10 +12081,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
-      <c r="S98" s="2" t="inlineStr"/>
-      <c r="T98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12111,7 +12143,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12139,32 +12171,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12172,7 +12208,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12196,17 +12232,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12216,17 +12252,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12254,32 +12290,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12287,7 +12327,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12311,17 +12351,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12331,17 +12371,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12442,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12484,12 +12524,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -12517,7 +12557,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12525,10 +12565,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q102" s="2" t="inlineStr"/>
-      <c r="R102" s="2" t="inlineStr"/>
-      <c r="S102" s="2" t="inlineStr"/>
-      <c r="T102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12571,7 +12627,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12632,7 +12688,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12686,7 +12742,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -12747,7 +12803,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12862,7 +12918,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12916,7 +12972,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -12977,7 +13033,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13031,7 +13087,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -13092,7 +13148,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13146,7 +13202,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -13207,7 +13263,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">

--- a/data/export/2026-09-28-浦东35路.xlsx
+++ b/data/export/2026-09-28-浦东35路.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2867,17 +2867,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3105,17 +3105,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5818,17 +5818,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8206,17 +8206,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9749,17 +9749,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10225,17 +10225,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12381,7 +12381,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12496,7 +12496,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12655,32 +12655,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12688,7 +12692,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12712,17 +12716,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12732,17 +12736,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -12770,32 +12774,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -12803,7 +12811,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12827,17 +12835,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12847,17 +12855,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -12885,32 +12893,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -12918,7 +12930,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12942,17 +12954,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12962,17 +12974,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -13033,7 +13045,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13087,7 +13099,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -13148,7 +13160,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13202,7 +13214,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13275,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
